--- a/Shared/XLS/CardSkill.xlsx
+++ b/Shared/XLS/CardSkill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -32,37 +32,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="121">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
-    <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -78,7 +70,7 @@
       </rPr>
       <t>ame</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -94,7 +86,7 @@
       </rPr>
       <t>esc</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -110,35 +102,35 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -154,67 +146,67 @@
       </rPr>
       <t>kill_01</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_1_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SourceGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RequiredCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CardSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>UltimateSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BuyPrice_Ultimate</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -509,231 +501,231 @@
   </si>
   <si>
     <t>SKILL_CARD_01_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_02_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_03_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_04_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_05_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_06_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_07_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_08_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_09_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_10_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_01_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_02_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_03_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_04_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_05_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_06_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_07_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_08_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_09_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_10_LV2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_01_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_02_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_03_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_04_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_05_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_06_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_07_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_08_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_09_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_10_LV3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_01_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_02_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_03_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_04_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_05_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_06_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_07_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_08_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_09_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_10_LV4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_01_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_02_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_03_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_04_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_05_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_06_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_07_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_08_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_09_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CARD_10_LV5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CardSkillGrade</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!CardSkillGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CardGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>TargetLevel</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaxShopLevel</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -761,27 +753,39 @@
       </rPr>
       <t>Enchant</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>UnlockClearDungeonID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -926,10 +930,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -945,17 +949,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -964,16 +968,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1254,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1274,36 +1278,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
-        <v>120</v>
+      <c r="B2" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
-        <v>6</v>
+      <c r="B6" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1340,10 +1344,10 @@
   <sheetData>
     <row r="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1354,115 +1358,115 @@
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="K2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="O3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="W3" s="10"/>
       <c r="X3" s="10"/>
@@ -1476,44 +1480,44 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2">
         <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K4" s="2">
         <v>150</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M4" s="2">
         <v>225</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O4" s="2">
         <v>350</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="2">
         <v>525</v>
@@ -1525,44 +1529,44 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>2</v>
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2">
         <v>100</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K5" s="2">
         <v>150</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M5" s="2">
         <v>225</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O5" s="2">
         <v>350</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q5" s="2">
         <v>525</v>
@@ -1574,44 +1578,44 @@
         <v>3</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K6" s="2">
         <v>150</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M6" s="2">
         <v>225</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O6" s="2">
         <v>350</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q6" s="2">
         <v>525</v>
@@ -1623,44 +1627,44 @@
         <v>4</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>2</v>
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2">
         <v>150</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M7" s="2">
         <v>225</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O7" s="2">
         <v>350</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q7" s="2">
         <v>525</v>
@@ -1672,44 +1676,44 @@
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I8" s="11">
         <v>200</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K8" s="2">
         <v>300</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M8" s="2">
         <v>450</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O8" s="2">
         <v>675</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q8" s="2">
         <v>1000</v>
@@ -1721,44 +1725,44 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I9" s="11">
         <v>200</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K9" s="2">
         <v>300</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M9" s="2">
         <v>450</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O9" s="2">
         <v>675</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q9" s="2">
         <v>1000</v>
@@ -1769,44 +1773,44 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="2">
         <v>300</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K10" s="2">
         <v>450</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M10" s="2">
         <v>675</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O10" s="2">
         <v>1000</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Q10" s="2">
         <v>1500</v>
@@ -1817,46 +1821,46 @@
         <v>8</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="11">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I11" s="2">
         <v>300</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K11" s="2">
         <v>450</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M11" s="2">
         <v>675</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O11" s="2">
         <v>1000</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q11" s="2">
         <v>1500</v>
@@ -1867,46 +1871,46 @@
         <v>9</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="11">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2">
         <v>400</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K12" s="2">
         <v>600</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>900</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O12" s="2">
         <v>1350</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q12" s="2">
         <v>2000</v>
@@ -1917,102 +1921,113 @@
         <v>10</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>6</v>
+        <v>59</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="G13" s="11">
         <v>2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I13" s="2">
         <v>600</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K13" s="2">
         <v>900</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M13" s="2">
         <v>1350</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O13" s="2">
         <v>2000</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Q13" s="2">
         <v>3000</v>
       </c>
     </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E16" s="11"/>
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="6:9" x14ac:dyDescent="0.3">
       <c r="I19"/>
     </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F20" s="11"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F21" s="11"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H30"/>
       <c r="I30"/>
     </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H31"/>
       <c r="I31"/>
     </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="6:9" x14ac:dyDescent="0.3">
       <c r="H32"/>
       <c r="I32"/>
     </row>
@@ -2045,7 +2060,7 @@
       <c r="I39"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2053,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -2076,10 +2091,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -2093,34 +2108,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
@@ -2133,8 +2148,8 @@
       <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>2</v>
+      <c r="C4" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D4" s="11">
         <v>1</v>
@@ -2152,8 +2167,8 @@
       <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>2</v>
+      <c r="C5" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D5" s="11">
         <v>2</v>
@@ -2171,8 +2186,8 @@
       <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>2</v>
+      <c r="C6" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D6" s="11">
         <v>3</v>
@@ -2190,8 +2205,8 @@
       <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>2</v>
+      <c r="C7" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D7" s="11">
         <v>4</v>
@@ -2209,8 +2224,8 @@
       <c r="B8" s="5">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>2</v>
+      <c r="C8" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D8" s="11">
         <v>5</v>
@@ -2228,8 +2243,8 @@
       <c r="B9" s="5">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>2</v>
+      <c r="C9" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D9" s="11">
         <v>6</v>
@@ -2247,8 +2262,8 @@
       <c r="B10" s="5">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>2</v>
+      <c r="C10" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D10" s="11">
         <v>7</v>
@@ -2266,8 +2281,8 @@
       <c r="B11" s="5">
         <v>8</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>2</v>
+      <c r="C11" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D11" s="11">
         <v>8</v>
@@ -2285,8 +2300,8 @@
       <c r="B12" s="5">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>2</v>
+      <c r="C12" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D12" s="11">
         <v>9</v>
@@ -2304,8 +2319,8 @@
       <c r="B13" s="5">
         <v>10</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>2</v>
+      <c r="C13" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D13" s="11">
         <v>10</v>
@@ -2324,7 +2339,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="11">
         <v>1</v>
@@ -2343,7 +2358,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="11">
         <v>2</v>
@@ -2362,7 +2377,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="11">
         <v>3</v>
@@ -2381,7 +2396,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="11">
         <v>4</v>
@@ -2400,7 +2415,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="11">
         <v>5</v>
@@ -2419,7 +2434,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="11">
         <v>6</v>
@@ -2438,7 +2453,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="11">
         <v>7</v>
@@ -2456,7 +2471,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="11">
         <v>8</v>
@@ -2474,7 +2489,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="11">
         <v>9</v>
@@ -2492,7 +2507,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="11">
         <v>10</v>
@@ -2510,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="11">
         <v>1</v>
@@ -2527,7 +2542,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="11">
         <v>2</v>
@@ -2544,7 +2559,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" s="11">
         <v>3</v>
@@ -2561,7 +2576,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="11">
         <v>4</v>
@@ -2578,7 +2593,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="11">
         <v>5</v>
@@ -2595,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" s="11">
         <v>6</v>
@@ -2612,7 +2627,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="11">
         <v>7</v>
@@ -2629,7 +2644,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" s="11">
         <v>8</v>
@@ -2646,7 +2661,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" s="11">
         <v>9</v>
@@ -2658,12 +2673,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="11">
         <v>10</v>
@@ -2675,12 +2690,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>31</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="11">
         <v>1</v>
@@ -2692,12 +2707,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>32</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" s="11">
         <v>2</v>
@@ -2709,12 +2724,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>33</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" s="11">
         <v>3</v>
@@ -2726,12 +2741,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>34</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" s="11">
         <v>4</v>
@@ -2742,13 +2757,14 @@
       <c r="F37" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>35</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" s="11">
         <v>5</v>
@@ -2759,13 +2775,14 @@
       <c r="F38" s="11">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>36</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="11">
         <v>6</v>
@@ -2776,13 +2793,14 @@
       <c r="F39" s="11">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="5">
         <v>37</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" s="11">
         <v>7</v>
@@ -2794,12 +2812,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>38</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" s="11">
         <v>8</v>
@@ -2811,12 +2829,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>39</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" s="11">
         <v>9</v>
@@ -2828,12 +2846,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>40</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" s="11">
         <v>10</v>
@@ -2845,12 +2863,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="5">
         <v>41</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D44" s="11">
         <v>1</v>
@@ -2862,12 +2880,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="5">
         <v>42</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45" s="11">
         <v>2</v>
@@ -2879,12 +2897,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="5">
         <v>43</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" s="11">
         <v>3</v>
@@ -2896,12 +2914,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="5">
         <v>44</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47" s="11">
         <v>4</v>
@@ -2913,12 +2931,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="5">
         <v>45</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" s="11">
         <v>5</v>
@@ -2935,7 +2953,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D49" s="11">
         <v>6</v>
@@ -2952,7 +2970,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" s="11">
         <v>7</v>
@@ -2969,7 +2987,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D51" s="11">
         <v>8</v>
@@ -2986,7 +3004,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52" s="11">
         <v>9</v>
@@ -3003,7 +3021,7 @@
         <v>50</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D53" s="11">
         <v>10</v>
@@ -3015,8 +3033,187 @@
         <v>5</v>
       </c>
     </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="5">
+        <v>51</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" s="11">
+        <v>1</v>
+      </c>
+      <c r="E54" s="11">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="5">
+        <v>52</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" s="11">
+        <v>2</v>
+      </c>
+      <c r="E55" s="11">
+        <v>2</v>
+      </c>
+      <c r="F55" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="5">
+        <v>53</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="11">
+        <v>3</v>
+      </c>
+      <c r="E56" s="11">
+        <v>3</v>
+      </c>
+      <c r="F56" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="5">
+        <v>54</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="11">
+        <v>4</v>
+      </c>
+      <c r="E57" s="11">
+        <v>4</v>
+      </c>
+      <c r="F57" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="5">
+        <v>55</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="11">
+        <v>5</v>
+      </c>
+      <c r="E58" s="11">
+        <v>5</v>
+      </c>
+      <c r="F58" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="5">
+        <v>56</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="11">
+        <v>6</v>
+      </c>
+      <c r="E59" s="11">
+        <v>6</v>
+      </c>
+      <c r="F59" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="5">
+        <v>57</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="11">
+        <v>7</v>
+      </c>
+      <c r="E60" s="11">
+        <v>7</v>
+      </c>
+      <c r="F60" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="5">
+        <v>58</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="11">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>8</v>
+      </c>
+      <c r="F61" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62" s="5">
+        <v>59</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" s="11">
+        <v>9</v>
+      </c>
+      <c r="E62" s="11">
+        <v>9</v>
+      </c>
+      <c r="F62" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="5">
+        <v>60</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="11">
+        <v>10</v>
+      </c>
+      <c r="E63" s="11">
+        <v>10</v>
+      </c>
+      <c r="F63" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C64" s="11"/>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="11"/>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="11"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/CardSkill.xlsx
+++ b/Shared/XLS/CardSkill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="122">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -765,6 +765,10 @@
   </si>
   <si>
     <t>Mythic</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CardSkillGrade</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1254,7 +1258,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1427,7 +1431,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>115</v>
